--- a/excel/镍.xlsx
+++ b/excel/镍.xlsx
@@ -1234,10 +1234,8 @@
         <f>IF(AND(ISNUMBER(T8),ISNUMBER(N8),N8&lt;&gt;0),(T8-N8)/N8,"-")</f>
         <v/>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>待发布(~8月上旬)</t>
-        </is>
+      <c r="V8" t="n">
+        <v>19900</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1246,7 +1244,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>新居滨电解镍满负荷,FY25电解镍创新高(~66.2kt);镍铁主动减产</t>
+          <t>26Q2(=FY2026Q1,2026年4-6月)镍合计19,900吨(环比-9.85%/同比-8.72%):电解镍15,100+硫酸镍3,700吨镍+水淬镍1,000吨镍;菲律宾NAC项目MSP 11,900吨镍(+23.96% QoQ)。决算8/7已发。源:Mysteel镍早读2026-08-19(新浪转载)+铁合金在线2026-08-12</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1256,7 +1254,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>25Q1由26Q1同比+9.95%反推;财年止3月,Mysteel按日历年重排｜23-25季度值以镍季度生产报告.xlsx为基准(公司镍合计=电解镍+硫酸镍+镍铁)</t>
+          <t>25Q1由26Q1同比+9.95%反推;财年止3月,Mysteel按日历年重排｜23-25季度值以镍季度生产报告.xlsx为基准(公司镍合计=电解镍+硫酸镍+镍铁)｜26Q2已按决算拆分入库(2026-08-31):合计19,900吨;注意25Q2=25,200为源表基准、公司口径约21,800,同比列暂不启用</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>待发布(~8月初)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1348,7 +1346,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026/2气旋Gezani停产近3个月,5月底酸厂重启;住友5/1签约出售54.17%权益给AMRI(零对价)</t>
+          <t>2026/2 气旋停产；住友已退出（6月交割 AMRI 54.17%+KOMIR），重启目标 6 月底；交割后无公开季报 → 26Q2 停产/未披露。源：mining.com 2026-05-01 + hsfkramer 2026-06-01</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1454,7 +1452,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>待发布(~8月)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1464,7 +1462,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>H1FY26(2025H2)9593吨(+14.5%):精炼去瓶颈+代炼增加</t>
+          <t>FY2026(止2026-06-30)全年精炼镍(gross refined and saleable)18,456吨(+17.6%)已披露(7/31产量报告,JSE SENS),无半年/季度拆分;9/3前后经审计年度业绩全文后复核→26Q2记-</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1474,7 +1472,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>不按季度披露镍,仅半年报/年报;FY25=15693｜公司不按季度披露镍;24季度为源表拆分值</t>
+          <t>不按季度披露镍,仅半年报/年报;FY25=15693｜公司不按季度披露镍;24季度为源表拆分值｜FY26全年18,456吨(7/31已披露),无日历季度拆分(2026-08-31核)</t>
         </is>
       </c>
     </row>
@@ -1658,10 +1656,8 @@
         <f>IF(AND(ISNUMBER(T12),ISNUMBER(N12),N12&lt;&gt;0),(T12-N12)/N12,"-")</f>
         <v/>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>待发布(8/12)</t>
-        </is>
+      <c r="V12" t="n">
+        <v>2638</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1670,7 +1666,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026/5美对古巴制裁扩大:暂停对Moa直接参与;Fort Saskatchewan精炼厂MSP库存6/22耗尽正关停</t>
+          <t>26Q2 Moa 成品镍权益口径 1,319 吨（同比-62%/环比-30%：古巴燃料及物资供应受限，Moa 矿山+Fort Saskatchewan 精炼厂停产检修）→ 100% 口径推算 2,638 吨（=权益×2，注明）。源：Sherritt Q2 2026 业绩（8/12）+华西证券点评</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2304,10 +2300,8 @@
         <f>IF(AND(ISNUMBER(T16),ISNUMBER(N16),N16&lt;&gt;0),(T16-N16)/N16,"-")</f>
         <v/>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>待发布(7/29)</t>
-        </is>
+      <c r="V4" t="n">
+        <v>8800</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -2316,7 +2310,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26Q1 +7%:Doniambo运行改善;矿石端-10%(东海岸矿点关闭);法政府TSDI 3.53亿欧元续命</t>
+          <t>26Q2 SLN 镍铁 8.8kt-Ni（环比-5%/同比持平）；H1 18.1kt（+3%）；现金成本 $8.5/lb（+6%，能源成本）。源：Eramet H1 2026 业绩附录 8（7/29）</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -2399,10 +2393,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>待发布(7/29)</t>
-        </is>
+      <c r="V5" t="n">
+        <v>7700</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -2411,7 +2403,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026初始RKAB仅批12Mwmt(外销9Mwmt,4月中用完),矿山5月起C&amp;M,冶炼靠库存维持;上调申请待批</t>
+          <t>26Q2 Weda Bay NPI 推算 7.7kt-Ni = H1 16.7kt（-2%）− Q1 9.0kt；RKAB 仅批 12Mwmt（-70%），4 月即用磬额度进入养护状态，NPI 厂靠库存维持。源：Eramet H1 2026（7/29）</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2696,10 +2688,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>待发布(~8月上旬)</t>
-        </is>
+      <c r="V8" t="n">
+        <v>1000</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -2708,12 +2698,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>按市况主动减产;推进镍铁转镍锍新产线(FY2027完工)</t>
+          <t>26Q2(=FY2026Q1,4-6月)Hyuga水淬镍1,000吨镍(Q1=900);决算8/7已发。源:Mysteel镍早读2026-08-19+铁合金在线2026-08-12</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>FY26镍铁4500吨</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>26Q2已入库(2026-08-31):1,000吨镍,与合计行勾稽(15,100+3,700+1,000=19,900)</t>
         </is>
       </c>
     </row>
@@ -2790,10 +2785,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>待发布(~7月底)</t>
-        </is>
+      <c r="V9" t="n">
+        <v>3812</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -2802,7 +2795,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26Q1 -11.6%:RKAB配额3月才全额批准+计划检修;2026指引+14%</t>
+          <t>26Q2 镍铁推算 3,812 TNi = H1 7,788 TNi（Petromindo）− Q1 3,976；Q2 镍铁销量 4,802 TNi（+420% 低基数）。源：Petromindo 2026-07-31 + indonesiaminer 8/3</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -3007,10 +3000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>待发布(~7月底-8月初)</t>
-        </is>
+      <c r="V11" t="n">
+        <v>19505</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -3019,7 +3010,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26Q1 +22.7%:2025两台炉大修完成低基数</t>
+          <t>26Q2 NPI（含 LGNM）19,505 tNi（+16% YoY）；SCM 矿石放量（SAP +130%/LIM +87%）；现金 margin $1,981/tNi（+11%）。FY26 指引：NPI 70-80kt。源：MBMA Q2 2026 运营公告（KONTAN 8/3）</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3146,9 +3137,14 @@
         <f>IF(AND(ISNUMBER(V12),ISNUMBER(O12),O12&lt;&gt;0),(V12-O12)/O12,"-")</f>
         <v/>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1H26中报已发(8/1),产量吨数未获取(官方简报PDF 12MB多次下载超时待补);HPAL销量H1=59,272吨镍(HPL+ONC)、FeNi销量同比+37%(无绝对值)、KPS三期建成新增6.5万吨镍/年产能→26Q2记-</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>季报（IDX）≈季后1个月；补印尼RKEF链缺口；2026-08-18新增骨架行，数据待回填</t>
+          <t>季报（IDX）≈季后1个月；补印尼RKEF链缺口；2026-08-18新增骨架行，数据待回填｜2026-08-31核:1H26中报已发,产量待补(PDF下载失败);HPAL销量H1=59,272吨镍</t>
         </is>
       </c>
     </row>
@@ -3247,27 +3243,28 @@
         <f>IF(AND(ISNUMBER(R13),ISNUMBER(M13),M13&lt;&gt;0),(R13-M13)/M13,"-")</f>
         <v/>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T13" t="n">
+        <v>432.5</v>
       </c>
       <c r="U13">
         <f>IF(AND(ISNUMBER(T13),ISNUMBER(N13),N13&lt;&gt;0),(T13-N13)/N13,"-")</f>
         <v/>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V13" t="n">
+        <v>432.5</v>
       </c>
       <c r="W13">
         <f>IF(AND(ISNUMBER(V13),ISNUMBER(O13),O13&lt;&gt;0),(V13-O13)/O13,"-")</f>
         <v/>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>H1 2026镍矿销量865万湿吨(+10%),26Q1/26Q2各432.5万湿吨(H1/2拟合,Q1未单独披露);归母净利P4.06bn(+93%)。源:NAC H1 2026业绩(philippine-resources 8/7+insiderph 8/6双源核)</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>季报（PSE）；菲律宾红土镍矿供应缺口；⚠矿石口径与板块金属量不同维，总计行勿加；2026-08-18新增骨架行，数据待回填</t>
+          <t>季报（PSE）；菲律宾红土镍矿供应缺口；⚠矿石口径与板块金属量不同维，总计行勿加；2026-08-18新增骨架行，数据待回填｜2026-08-31核:865万湿吨与行口径(矿石销量万湿吨)一致,非金属量;两季平分拟合</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3755,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>待发布(~7月底-8月初)</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -3768,7 +3765,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025/10复产后稳定;现金成本$14029/t但售价+14%利润率大增</t>
+          <t>MBMA Q2 2026 公告（8/3）仅披露 NPI 19,505 tNi 与 PT ESG MHP 4,831 吨；HGNM 高冰镍分季产量未披露（仅年度指引 44-48kt）→ 未找到。源：KONTAN 2026-08-03</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -3882,6 +3879,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>-</t>
@@ -4009,7 +4011,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>待发布(中报8月)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -4019,7 +4021,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025产量28.7万金属吨(+49%),MHP出货23.7万吨(+30%);华飞12万吨HPAL 2026/4起停产检修拖累Q2</t>
+          <t>2026中报已披露(8月),未披露镍产量吨数→26Q2记-;华飞12万吨HPAL 2026/4起停产检修仍拖累</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -4029,7 +4031,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>A股季报不披露产量;100%项目口径,权益约13-16.5万吨(券商估)｜2025年报：镍产品毛利率19.7%(-7.4pct)、镍中间品19.0%(-2.9pct，镍价跌+硫磺涨)；经营现金流40.1亿(-68%，主动囤货)vs净利61.1亿；capex 106.6亿(+59%)</t>
+          <t>A股季报不披露产量;100%项目口径,权益约13-16.5万吨(券商估)｜2025年报：镍产品毛利率19.7%(-7.4pct)、镍中间品19.0%(-2.9pct，镍价跌+硫磺涨)；经营现金流40.1亿(-68%，主动囤货)vs净利61.1亿；capex 106.6亿(+59%)｜2026中报已披露(8月),未披露镍产量吨数(2026-08-31核)</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4139,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>待发布(中报8月)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -4147,7 +4149,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中青富氧侧吹全球首条工业化产线,规划6万金吨</t>
+          <t>中报(8/25)仅披露新能源金属(镍产品)板块口径H1=126,081.84金吨(利用率92.03%),为电解镍/高冰镍/镍铁灵活切换的板块合计,非MHP/高冰镍中间品口径,与本行口径不符不入库→26Q2记-</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -4157,7 +4159,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>官方未给单一产量数;25权益出货约10万吨/26Q1约3万吨均为东吴测算,规划产能19.5万金吨｜2025年报(H股口径)：新能源金属产品收入178亿(+32%)，产21.77万/销23.25万金吨(+41%/+58%)，产能利用率91.2%；毛利率未单列(定性盈利有限)</t>
+          <t>官方未给单一产量数;25权益出货约10万吨/26Q1约3万吨均为东吴测算,规划产能19.5万金吨｜2025年报(H股口径)：新能源金属产品收入178亿(+32%)，产21.77万/销23.25万金吨(+41%/+58%)，产能利用率91.2%；毛利率未单列(定性盈利有限)｜2026中报已发(8/25),板块口径H1=126,081.84金吨非中间品口径不入库(2026-08-31核)</t>
         </is>
       </c>
     </row>
@@ -4255,20 +4257,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>未披露</t>
-        </is>
+      <c r="T7" t="n">
+        <v>13895</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>待发布(中报8月)</t>
-        </is>
+      <c r="V7" t="n">
+        <v>13895</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -4277,7 +4275,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025 MHP出货超11万吨镍(+110%);15万吨/年产能2025/7起满产;6万吨电积镍产能释放</t>
+          <t>中报(8/27):海外镍项目(MHP)H1镍产出27,790吨(含参股产能口径,同比-37%,为计划量40%)→26Q1=26Q2=13,895(H1/2拟合);2H26公司计划65,000吨</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -4287,7 +4285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>出货口径含参股;26Q1「近2万吨」为自媒体口径慎用｜修正为年报精确值110,839吨(+114%)；2025镍资源板块收入73.29亿(+25.3%)、毛利率18.13%；有息负债超300亿(资产负债率65.8%)</t>
+          <t>出货口径含参股;26Q1「近2万吨」为自媒体口径慎用｜修正为年报精确值110,839吨(+114%)；2025镍资源板块收入73.29亿(+25.3%)、毛利率18.13%；有息负债超300亿(资产负债率65.8%)｜2026-08-31入库:H1累计27,790吨含参股口径,Q1未披露,两季平分拟合;2H26计划65,000吨</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4397,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>待发布(中报~8月下旬)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -4409,7 +4407,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>湿法12万金属吨产能全年满负荷;KPS二期6线达产;2026 KPS 12线全部达产;A股IPO 7/10提交注册</t>
+          <t>2026中期业绩已披露(8/27,港交所),未披露Obi HPAL/镍铁产量或销量吨数(惯例如此);产能锚点总40万镍金属吨,KPS 12条线8/1全面达产、湿法满产→26Q2记-</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4419,7 +4417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>年报仅销量/产能口径:MHP销量47.16万湿吨(+122%),镍铁69.81万实物吨;产量金属吨未直接披露｜2025年报：湿法(镍钴化合物)毛利率39.3%(-3.5pct，硫磺涨价)、火法镍铁14.6%(收入+406%以量补价)；汇兑亏损4.51亿+支柱二补税4.05亿；MHP 47.16万湿吨≈折镍8-9万金属吨(与12万吨产能满产勾稽一致)</t>
+          <t>年报仅销量/产能口径:MHP销量47.16万湿吨(+122%),镍铁69.81万实物吨;产量金属吨未直接披露｜2025年报：湿法(镍钴化合物)毛利率39.3%(-3.5pct，硫磺涨价)、火法镍铁14.6%(收入+406%以量补价)；汇兑亏损4.51亿+支柱二补税4.05亿；MHP 47.16万湿吨≈折镍8-9万金属吨(与12万吨产能满产勾稽一致)｜2026中期业绩已披露(8/27)未披露产量吨数;产能锚点40万金吨镍,KPS 8/1全面达产(2026-08-31核)</t>
         </is>
       </c>
     </row>
@@ -4523,10 +4521,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>待发布(8/12)</t>
-        </is>
+      <c r="V9" t="n">
+        <v>934</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>古巴燃料断供+美制裁:26Q1 -43%;精炼厂关停中</t>
+          <t>26Q2 Moa MSP 权益产量 934 吨（古巴燃料/物资受限，停产检修）；权益口径（50%）。源：Sherritt Q2 2026（8/12）+华西证券点评</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4662,9 +4658,14 @@
         <f>IF(AND(ISNUMBER(V10),ISNUMBER(O10),O10&lt;&gt;0),(V10-O10)/O10,"-")</f>
         <v/>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1H26中报已发(8/1),HPAL产量吨数未获取(官方PDF下载失败待补);HPAL销量H1=59,272吨镍(HPL+ONC)→26Q2记-</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>季报（IDX）≈季后1个月；补印尼HPAL链缺口；与NPI行同公司不同板块；2026-08-18新增骨架行，数据待回填</t>
+          <t>季报（IDX）≈季后1个月；补印尼HPAL链缺口；与NPI行同公司不同板块；2026-08-18新增骨架行，数据待回填｜2026-08-31核:1H26中报已发,产量待补;HPAL销量H1=59,272吨镍</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4769,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4931,6 +4931,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>镍 26Q2 欠账补录：Eramet SLN 8800/Weda Bay 7700（推算）；Sherritt 2638（100%推算）+MSP 934；Antam 3812（推算）；MBMA 19505；Ambatovy 停产未披露；住友/Harita 待拆/待发布；NAC H1=865 万湿吨</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eramet H1（7/29）；Sherritt Q2（8/12）；Petromindo/KONTAN；NAC H1（8/7）；mining.com/HSF（Ambatovy）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/镍.xlsx
+++ b/excel/镍.xlsx
@@ -3753,10 +3753,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
+      <c r="V3" t="n">
+        <v>9165</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -3765,7 +3763,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>MBMA Q2 2026 公告（8/3）仅披露 NPI 19,505 tNi 与 PT ESG MHP 4,831 吨；HGNM 高冰镍分季产量未披露（仅年度指引 44-48kt）→ 未找到。源：KONTAN 2026-08-03</t>
+          <t>26Q2 HGNM 高冰镍 9,165 tNiEq（-12% QoQ，销量 10,457 tNiEq +30%；ASP $15,811/tNi，现金成本 $16,354/tNi，单吨转负 margin -$542）；同季报：NPI 19,505 tNi（+16% YoY）、PT ESG MHP 4,831 吨镍（8 月目标达产）、SLNC 9 万吨 HPAL 在建。源：MBMA Q2 2026 Quarterly Activities Report（merdekabattery.com，2026-08-01）；8/24 仅据 KONTAN 综述误标'未找到'，本次按官方原文更正</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -3879,10 +3877,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="V4" t="n">
+        <v>19646</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -3891,7 +3887,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26Q2产量未披露(销量17,824吨镍)；ENC 7/21产首批MHP，首批镍阴极预计8月中</t>
+          <t>26Q2=19,646吨镍（推算：H1'26 官方 41,172 − Q1 官方 21,526；半年报 Directors' Report 披露）；Q2 季报仅直接披露销量（权益口径 1.8ktNi，总销量约 1.8 万吨）；HNC EBITDA $14.4m、首次分红 $3.5m；ENC 7 月产出首批 MHP（权益 46%）。源：NIC H1'26  interim report + Q2'26 Quarterly Activities Report（7/29）</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -3901,7 +3897,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>权益仅10%;另有钴2370吨(26Q1)</t>
+          <t>权益仅10%；另有钴(26Q1=2,370吨)；26Q2=19,646为官方 H1−Q1 推算值（2026-10-14入库）；26Q1 同比公式引用基准列为'-'故同比显示-</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4948,6 +4944,40 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>26Q2复核：中伟——2026中报(8/25)新能源金属H1产量126,081.84金吨(有效产能13.7万/利用率92.03%)为板块合计口径，与本行权益中间品口径不符，26Q2维持"-"（8/31已记，本次复核确认）</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中伟新材2026半年度报告全文（新浪财经/巨潮）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>镍 26Q2 缺口收口：NIC HNC MHP 26Q2=19,646（官方 H1 41,172−Q1 21,526 推算，交叉验证 RKEF H1=58,128=Q1+Q2 吻合）；MBMA HGNM 26Q2=9,165（官方季报直接披露，更正 8/24 '未找到'）；Ambatovy 维持'-'（2月气旋停产+6月交割 AMRI，无季报）；Implats 维持'-'（FY26 全年 18,456 吨已披露 7/31，无季度拆分）；South32 Cerro Matoso 维持'-'（2025/12/1 售 CoreX，退出披露）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NIC H1 2026 interim report（nickelindustries.com）+ Q2'26 Quarterly Activities Report/Presentation（2026-07-29）；MBMA Q2 2026 Quarterly Activities Report（merdekabattery.com，2026-08-01）；Implats FY26 产量报告（JSE SENS 7/31）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
